--- a/Project/outputs/tables/table_master_comparison.xlsx
+++ b/Project/outputs/tables/table_master_comparison.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,34 +51,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -454,723 +426,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>VAR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+          <t>VAR_h1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h10</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h22</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
+          <t>LSTM_h1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h10</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h22</t>
+        </is>
+      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
+          <t>GRU_h1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Horizon</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.000874 (8.1%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.003947 (20.0%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.010610 (31.1%)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.027291 (47.8%)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.000489 (7.7%)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.003408 (25.1%)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.008592 (31.6%)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.025878 (41.2%)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.000381 (6.1%)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.003101 (15.8%)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.009471 (28.7%)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.026552 (39.3%)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Market</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DAX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.000747 (8.6%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.002569 (20.1%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.006701 (31.4%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.016685 (45.1%)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.000451 (7.3%)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.001926 (17.3%)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.004530 (26.2%)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.016190 (45.1%)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.000395 (5.9%)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.002010 (17.9%)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.004580 (25.5%)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.015260 (39.5%)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAC 40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000823 (8.9%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002979 (21.3%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007629 (34.1%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.018674 (48.7%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000489 (7.8%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002383 (21.6%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005214 (34.9%)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.016720 (48.5%)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000421 (6.0%)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002091 (21.0%)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005694 (35.5%)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.016584 (42.8%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FTSE 100</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000550 (8.0%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001958 (18.0%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004870 (25.6%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.012988 (36.7%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000328 (6.5%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001590 (18.2%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003503 (23.5%)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.012059 (31.1%)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000266 (5.3%)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001973 (18.3%)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003715 (22.6%)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.012161 (29.7%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nikkei</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000499 (7.6%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001530 (15.9%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002531 (20.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006911 (30.2%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000243 (5.4%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001255 (12.9%)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002280 (23.9%)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006247 (25.5%)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000239 (5.2%)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001482 (15.2%)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001892 (18.0%)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007046 (31.0%)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000535 (6.9%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002145 (15.2%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005099 (24.4%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.015166 (39.8%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000288 (5.6%)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001869 (13.7%)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002815 (22.7%)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.011157 (26.8%)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000277 (6.9%)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001265 (13.9%)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003529 (22.8%)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.015057 (30.2%)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hang Seng</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000381 (6.6%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001313 (14.2%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003000 (21.3%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007936 (31.5%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000501 (5.9%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001798 (15.5%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003303 (21.1%)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004812 (22.4%)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000233 (5.1%)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001894 (15.4%)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002503 (19.9%)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006226 (25.5%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000509 (7.2%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001478 (14.6%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002851 (22.6%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005508 (37.8%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000234 (6.6%)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001417 (19.4%)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003377 (33.5%)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006051 (49.2%)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000194 (4.8%)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001014 (13.7%)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002421 (25.5%)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007904 (53.2%)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000615 (7.7%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002240 (17.4%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005411 (26.4%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.013895 (39.7%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000378 (6.6%)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001956 (18.0%)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004202 (27.2%)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.012389 (36.2%)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000301 (5.7%)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001854 (16.4%)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004226 (24.8%)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0.013349 (36.4%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1181,723 +1110,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>VAR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+          <t>VAR_h1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h10</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>VAR_h22</t>
+        </is>
+      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
+          <t>LSTM_h1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h10</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LSTM_h22</t>
+        </is>
+      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
+          <t>GRU_h1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>GRU_h22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Horizon</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>h=10</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.000340 (6.7%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.001328 (14.9%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.002953 (23.6%)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.006549 (36.6%)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.000212 (5.7%)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.001529 (15.0%)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.003610 (21.3%)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.005887 (25.6%)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.000172 (4.9%)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.002579 (21.7%)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.003425 (20.7%)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.004986 (25.7%)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Market</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DAX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.000466 (7.5%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.001591 (16.2%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.003228 (24.8%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.006413 (39.2%)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.000199 (7.2%)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.001040 (15.8%)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.001806 (21.9%)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.003979 (40.8%)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.000182 (5.9%)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.000850 (14.3%)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.001669 (19.8%)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.003545 (37.0%)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAC 40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000394 (7.6%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001419 (16.8%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002940 (24.9%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005947 (38.9%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000139 (6.1%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001073 (18.3%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001691 (23.6%)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004059 (42.2%)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000136 (5.4%)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000822 (15.5%)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001892 (25.0%)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002539 (28.9%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FTSE 100</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000278 (7.8%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001139 (18.0%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002502 (29.7%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004968 (49.9%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000172 (10.2%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001319 (28.8%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001556 (27.6%)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002947 (44.4%)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000122 (7.4%)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000739 (18.2%)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001619 (30.1%)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002932 (47.2%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nikkei</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000991 (6.9%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003965 (15.0%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007626 (22.0%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.013698 (31.4%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000439 (5.0%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003696 (14.3%)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007770 (28.4%)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.011680 (25.3%)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000421 (5.0%)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003443 (16.0%)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007153 (21.1%)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.012476 (40.5%)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000557 (7.1%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001938 (15.9%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003795 (23.5%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006473 (33.2%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000283 (5.5%)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001808 (15.2%)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003435 (22.7%)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005861 (24.6%)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000362 (7.2%)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001662 (14.2%)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004228 (23.6%)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006586 (27.6%)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hang Seng</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001179 (6.7%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003672 (13.2%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006402 (18.1%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.011496 (24.5%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000586 (5.5%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003126 (14.5%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005584 (19.1%)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.011148 (26.7%)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000533 (4.9%)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004080 (18.6%)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.005316 (18.4%)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.011861 (31.2%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000505 (8.3%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001775 (19.1%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003063 (30.0%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004969 (47.4%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000301 (8.1%)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002293 (29.6%)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004258 (45.6%)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006862 (64.8%)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000241 (5.9%)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001504 (20.4%)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003119 (35.6%)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.008471 (67.5%)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000589 (7.3%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.002103 (16.1%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.004064 (24.6%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.007564 (37.6%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000291 (6.7%)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001986 (18.9%)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003714 (26.3%)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.006553 (36.8%)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.000271 (5.8%)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001960 (17.3%)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.003553 (24.3%)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CSI 300</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0.006674 (38.2%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>